--- a/16-CONTAS-A-PAGAR-2026-08-31.xlsx
+++ b/16-CONTAS-A-PAGAR-2026-08-31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandre\Documents\Gemini-Cli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{091023A6-09BE-4D00-ACAE-FB84FBC90428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2B5E9D-D0FE-4180-96D5-5117FD5C9431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7B33E2D-C36E-468D-A068-F93D1BCD6287}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="215">
   <si>
     <t>Dt.Ref: 31/08/2026</t>
   </si>
@@ -674,14 +674,17 @@
     <t>PR - DAMSP/OACO 61237790000118/ RECEITA:TFE /CCM 4.341.913-5/INCIDENCIA:____/_____/VENC ______ COD BOL=</t>
   </si>
   <si>
-    <t>SEM PA</t>
+    <t>A PAGAR:</t>
+  </si>
+  <si>
+    <t>A PAGAR SEM PA:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Courier New"/>
@@ -797,13 +800,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -983,6 +981,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -1153,19 +1157,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1174,10 +1178,25 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1581,7 +1600,8 @@
     <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="190.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4.5703125" bestFit="1" customWidth="1"/>
@@ -1661,7 +1681,7 @@
       <c r="P4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R4" s="1" t="s">
@@ -1750,7 +1770,7 @@
       <c r="I5" s="2">
         <v>46099</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="6">
         <v>0.01</v>
       </c>
       <c r="K5" s="3" t="s">
@@ -1771,7 +1791,7 @@
       <c r="P5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="Q5" s="6">
         <v>0.01</v>
       </c>
       <c r="R5" s="4">
@@ -1860,7 +1880,7 @@
       <c r="I6" s="2">
         <v>46164</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="6">
         <v>300</v>
       </c>
       <c r="K6" s="3" t="s">
@@ -1881,7 +1901,7 @@
       <c r="P6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="6">
         <v>300</v>
       </c>
       <c r="R6" s="4">
@@ -1942,223 +1962,223 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+    <row r="7" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
         <v>46246</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="8">
         <v>46246</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="8">
         <v>46246</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="10">
         <v>300</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="L7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="3" t="s">
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="10">
         <v>300</v>
       </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
+      <c r="R7" s="11">
+        <v>0</v>
+      </c>
+      <c r="S7" s="11">
+        <v>0</v>
+      </c>
+      <c r="T7" s="11">
+        <v>0</v>
+      </c>
+      <c r="U7" s="12">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W7" s="4">
-        <v>0</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB7" s="3" t="s">
+      <c r="V7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="W7" s="11">
+        <v>0</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="AC7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF7" s="3" t="s">
+      <c r="AC7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AG7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ7" s="3" t="s">
+      <c r="AG7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ7" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+    <row r="8" spans="1:36" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
         <v>46259</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="8">
         <v>46259</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="8">
         <v>46259</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="10">
         <v>15063.5</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="3" t="s">
+      <c r="L8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="Q8" s="10">
         <v>15063.5</v>
       </c>
-      <c r="R8" s="4">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5">
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
+        <v>0</v>
+      </c>
+      <c r="U8" s="12">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W8" s="4">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB8" s="3" t="s">
+      <c r="V8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="W8" s="11">
+        <v>0</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF8" s="3" t="s">
+      <c r="AC8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AG8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ8" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2190,7 +2210,7 @@
       <c r="I9" s="2">
         <v>46267</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="6">
         <v>5541.51</v>
       </c>
       <c r="K9" s="3" t="s">
@@ -2211,7 +2231,7 @@
       <c r="P9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="Q9" s="6">
         <v>5541.51</v>
       </c>
       <c r="R9" s="4">
@@ -2321,7 +2341,7 @@
       <c r="P10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="Q10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R10" s="1" t="s">
@@ -2410,7 +2430,7 @@
       <c r="I11" s="2">
         <v>46267</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="6">
         <v>973.5</v>
       </c>
       <c r="K11" s="3" t="s">
@@ -2431,7 +2451,7 @@
       <c r="P11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="Q11" s="6">
         <v>973.5</v>
       </c>
       <c r="R11" s="4">
@@ -2520,7 +2540,7 @@
       <c r="I12" s="2">
         <v>46269</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="6">
         <v>4361</v>
       </c>
       <c r="K12" s="3" t="s">
@@ -2541,7 +2561,7 @@
       <c r="P12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="6">
         <v>4361</v>
       </c>
       <c r="R12" s="4">
@@ -2630,7 +2650,7 @@
       <c r="I13" s="2">
         <v>46269</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="6">
         <v>350</v>
       </c>
       <c r="K13" s="3" t="s">
@@ -2651,7 +2671,7 @@
       <c r="P13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="Q13" s="6">
         <v>350</v>
       </c>
       <c r="R13" s="4">
@@ -2740,7 +2760,7 @@
       <c r="I14" s="2">
         <v>46269</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <v>428.17</v>
       </c>
       <c r="K14" s="3" t="s">
@@ -2761,7 +2781,7 @@
       <c r="P14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="Q14" s="6">
         <v>428.17</v>
       </c>
       <c r="R14" s="4">
@@ -2850,7 +2870,7 @@
       <c r="I15" s="2">
         <v>46273</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="6">
         <v>1853.33</v>
       </c>
       <c r="K15" s="3" t="s">
@@ -2871,7 +2891,7 @@
       <c r="P15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="Q15" s="6">
         <v>1853.33</v>
       </c>
       <c r="R15" s="4">
@@ -2960,7 +2980,7 @@
       <c r="I16" s="2">
         <v>46273</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="6">
         <v>330</v>
       </c>
       <c r="K16" s="3" t="s">
@@ -2981,7 +3001,7 @@
       <c r="P16" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="6">
         <v>330</v>
       </c>
       <c r="R16" s="4">
@@ -3091,7 +3111,7 @@
       <c r="P17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="Q17" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R17" s="1" t="s">
@@ -3180,7 +3200,7 @@
       <c r="I18" s="2">
         <v>46273</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <v>4706.62</v>
       </c>
       <c r="K18" s="3" t="s">
@@ -3201,7 +3221,7 @@
       <c r="P18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="Q18" s="6">
         <v>4706.62</v>
       </c>
       <c r="R18" s="4">
@@ -3290,7 +3310,7 @@
       <c r="I19" s="2">
         <v>46273</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="6">
         <v>454</v>
       </c>
       <c r="K19" s="3" t="s">
@@ -3311,7 +3331,7 @@
       <c r="P19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="Q19" s="6">
         <v>454</v>
       </c>
       <c r="R19" s="4">
@@ -3400,7 +3420,7 @@
       <c r="I20" s="2">
         <v>46273</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="6">
         <v>4556.91</v>
       </c>
       <c r="K20" s="3" t="s">
@@ -3421,7 +3441,7 @@
       <c r="P20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="Q20" s="6">
         <v>4556.91</v>
       </c>
       <c r="R20" s="4">
@@ -3510,7 +3530,7 @@
       <c r="I21" s="2">
         <v>46275</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="6">
         <v>1864.7</v>
       </c>
       <c r="K21" s="3" t="s">
@@ -3531,7 +3551,7 @@
       <c r="P21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="Q21" s="6">
         <v>1864.7</v>
       </c>
       <c r="R21" s="4">
@@ -3620,7 +3640,7 @@
       <c r="I22" s="2">
         <v>46275</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <v>7850</v>
       </c>
       <c r="K22" s="3" t="s">
@@ -3641,7 +3661,7 @@
       <c r="P22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="Q22" s="6">
         <v>7850</v>
       </c>
       <c r="R22" s="4">
@@ -3730,7 +3750,7 @@
       <c r="I23" s="2">
         <v>46275</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="6">
         <v>15000</v>
       </c>
       <c r="K23" s="3" t="s">
@@ -3751,7 +3771,7 @@
       <c r="P23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="Q23" s="6">
         <v>15000</v>
       </c>
       <c r="R23" s="4">
@@ -3861,7 +3881,7 @@
       <c r="P24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="Q24" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R24" s="1" t="s">
@@ -3950,7 +3970,7 @@
       <c r="I25" s="2">
         <v>46275</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="6">
         <v>5400</v>
       </c>
       <c r="K25" s="3" t="s">
@@ -3971,7 +3991,7 @@
       <c r="P25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="Q25" s="6">
         <v>5400</v>
       </c>
       <c r="R25" s="4">
@@ -4060,7 +4080,7 @@
       <c r="I26" s="2">
         <v>46276</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="6">
         <v>926.67</v>
       </c>
       <c r="K26" s="3" t="s">
@@ -4081,7 +4101,7 @@
       <c r="P26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="Q26" s="6">
         <v>926.67</v>
       </c>
       <c r="R26" s="4">
@@ -4170,7 +4190,7 @@
       <c r="I27" s="2">
         <v>46279</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="6">
         <v>3100</v>
       </c>
       <c r="K27" s="3" t="s">
@@ -4191,7 +4211,7 @@
       <c r="P27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="Q27" s="6">
         <v>3100</v>
       </c>
       <c r="R27" s="4">
@@ -4280,7 +4300,7 @@
       <c r="I28" s="2">
         <v>46280</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="6">
         <v>10000</v>
       </c>
       <c r="K28" s="3" t="s">
@@ -4301,7 +4321,7 @@
       <c r="P28" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="Q28" s="6">
         <v>10000</v>
       </c>
       <c r="R28" s="4">
@@ -4390,7 +4410,7 @@
       <c r="I29" s="2">
         <v>46280</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="6">
         <v>99</v>
       </c>
       <c r="K29" s="3" t="s">
@@ -4411,7 +4431,7 @@
       <c r="P29" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="Q29" s="6">
         <v>99</v>
       </c>
       <c r="R29" s="4">
@@ -4500,7 +4520,7 @@
       <c r="I30" s="2">
         <v>46280</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="6">
         <v>1621</v>
       </c>
       <c r="K30" s="3" t="s">
@@ -4521,7 +4541,7 @@
       <c r="P30" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="Q30" s="6">
         <v>1621</v>
       </c>
       <c r="R30" s="4">
@@ -4631,7 +4651,7 @@
       <c r="P31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="Q31" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R31" s="1" t="s">
@@ -4720,7 +4740,7 @@
       <c r="I32" s="2">
         <v>46280</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="6">
         <v>650</v>
       </c>
       <c r="K32" s="3" t="s">
@@ -4741,7 +4761,7 @@
       <c r="P32" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="Q32" s="4">
+      <c r="Q32" s="6">
         <v>650</v>
       </c>
       <c r="R32" s="4">
@@ -4830,7 +4850,7 @@
       <c r="I33" s="2">
         <v>46280</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="6">
         <v>150</v>
       </c>
       <c r="K33" s="3" t="s">
@@ -4851,7 +4871,7 @@
       <c r="P33" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="Q33" s="6">
         <v>150</v>
       </c>
       <c r="R33" s="4">
@@ -4940,7 +4960,7 @@
       <c r="I34" s="2">
         <v>46280</v>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="6">
         <v>980</v>
       </c>
       <c r="K34" s="3" t="s">
@@ -4961,7 +4981,7 @@
       <c r="P34" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="Q34" s="4">
+      <c r="Q34" s="6">
         <v>980</v>
       </c>
       <c r="R34" s="4">
@@ -5050,7 +5070,7 @@
       <c r="I35" s="2">
         <v>46280</v>
       </c>
-      <c r="J35" s="8">
+      <c r="J35" s="6">
         <v>179.18</v>
       </c>
       <c r="K35" s="3" t="s">
@@ -5071,7 +5091,7 @@
       <c r="P35" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="Q35" s="4">
+      <c r="Q35" s="6">
         <v>179.18</v>
       </c>
       <c r="R35" s="4">
@@ -5160,7 +5180,7 @@
       <c r="I36" s="2">
         <v>46280</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="6">
         <v>154.1</v>
       </c>
       <c r="K36" s="3" t="s">
@@ -5181,7 +5201,7 @@
       <c r="P36" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="Q36" s="4">
+      <c r="Q36" s="6">
         <v>154.1</v>
       </c>
       <c r="R36" s="4">
@@ -5270,7 +5290,7 @@
       <c r="I37" s="2">
         <v>46280</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="6">
         <v>657.9</v>
       </c>
       <c r="K37" s="3" t="s">
@@ -5291,7 +5311,7 @@
       <c r="P37" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="Q37" s="6">
         <v>657.9</v>
       </c>
       <c r="R37" s="4">
@@ -5401,7 +5421,7 @@
       <c r="P38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="Q38" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R38" s="1" t="s">
@@ -5490,7 +5510,7 @@
       <c r="I39" s="2">
         <v>46283</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="6">
         <v>157.29</v>
       </c>
       <c r="K39" s="3" t="s">
@@ -5511,7 +5531,7 @@
       <c r="P39" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="Q39" s="4">
+      <c r="Q39" s="6">
         <v>157.29</v>
       </c>
       <c r="R39" s="4">
@@ -5600,7 +5620,7 @@
       <c r="I40" s="2">
         <v>46286</v>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="6">
         <v>1853.33</v>
       </c>
       <c r="K40" s="3" t="s">
@@ -5621,7 +5641,7 @@
       <c r="P40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q40" s="4">
+      <c r="Q40" s="6">
         <v>1853.33</v>
       </c>
       <c r="R40" s="4">
@@ -5710,7 +5730,7 @@
       <c r="I41" s="2">
         <v>46286</v>
       </c>
-      <c r="J41" s="8">
+      <c r="J41" s="6">
         <v>2400</v>
       </c>
       <c r="K41" s="3" t="s">
@@ -5731,7 +5751,7 @@
       <c r="P41" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="Q41" s="4">
+      <c r="Q41" s="6">
         <v>2400</v>
       </c>
       <c r="R41" s="4">
@@ -5820,7 +5840,7 @@
       <c r="I42" s="2">
         <v>46286</v>
       </c>
-      <c r="J42" s="8">
+      <c r="J42" s="6">
         <v>621</v>
       </c>
       <c r="K42" s="3" t="s">
@@ -5841,7 +5861,7 @@
       <c r="P42" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="Q42" s="4">
+      <c r="Q42" s="6">
         <v>621</v>
       </c>
       <c r="R42" s="4">
@@ -5930,7 +5950,7 @@
       <c r="I43" s="2">
         <v>46286</v>
       </c>
-      <c r="J43" s="8">
+      <c r="J43" s="6">
         <v>2969.75</v>
       </c>
       <c r="K43" s="3" t="s">
@@ -5951,7 +5971,7 @@
       <c r="P43" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="Q43" s="4">
+      <c r="Q43" s="6">
         <v>2969.75</v>
       </c>
       <c r="R43" s="4">
@@ -6040,7 +6060,7 @@
       <c r="I44" s="2">
         <v>46286</v>
       </c>
-      <c r="J44" s="8">
+      <c r="J44" s="6">
         <v>343.13</v>
       </c>
       <c r="K44" s="3" t="s">
@@ -6061,7 +6081,7 @@
       <c r="P44" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="Q44" s="4">
+      <c r="Q44" s="6">
         <v>343.13</v>
       </c>
       <c r="R44" s="4">
@@ -6171,7 +6191,7 @@
       <c r="P45" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q45" s="1" t="s">
+      <c r="Q45" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R45" s="1" t="s">
@@ -6260,7 +6280,7 @@
       <c r="I46" s="2">
         <v>46286</v>
       </c>
-      <c r="J46" s="8">
+      <c r="J46" s="6">
         <v>20000</v>
       </c>
       <c r="K46" s="3" t="s">
@@ -6281,7 +6301,7 @@
       <c r="P46" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="Q46" s="4">
+      <c r="Q46" s="6">
         <v>20000</v>
       </c>
       <c r="R46" s="4">
@@ -6370,7 +6390,7 @@
       <c r="I47" s="2">
         <v>46286</v>
       </c>
-      <c r="J47" s="8">
+      <c r="J47" s="6">
         <v>1100</v>
       </c>
       <c r="K47" s="3" t="s">
@@ -6391,7 +6411,7 @@
       <c r="P47" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="Q47" s="4">
+      <c r="Q47" s="6">
         <v>1100</v>
       </c>
       <c r="R47" s="4">
@@ -6480,7 +6500,7 @@
       <c r="I48" s="2">
         <v>46286</v>
       </c>
-      <c r="J48" s="8">
+      <c r="J48" s="6">
         <v>5400</v>
       </c>
       <c r="K48" s="3" t="s">
@@ -6501,7 +6521,7 @@
       <c r="P48" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q48" s="4">
+      <c r="Q48" s="6">
         <v>5400</v>
       </c>
       <c r="R48" s="4">
@@ -6590,7 +6610,7 @@
       <c r="I49" s="2">
         <v>46286</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="6">
         <v>119.99</v>
       </c>
       <c r="K49" s="3" t="s">
@@ -6611,7 +6631,7 @@
       <c r="P49" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="Q49" s="4">
+      <c r="Q49" s="6">
         <v>119.99</v>
       </c>
       <c r="R49" s="4">
@@ -6700,7 +6720,7 @@
       <c r="I50" s="2">
         <v>46286</v>
       </c>
-      <c r="J50" s="8">
+      <c r="J50" s="6">
         <v>973.5</v>
       </c>
       <c r="K50" s="3" t="s">
@@ -6721,7 +6741,7 @@
       <c r="P50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q50" s="4">
+      <c r="Q50" s="6">
         <v>973.5</v>
       </c>
       <c r="R50" s="4">
@@ -6810,7 +6830,7 @@
       <c r="I51" s="2">
         <v>46288</v>
       </c>
-      <c r="J51" s="8">
+      <c r="J51" s="6">
         <v>922</v>
       </c>
       <c r="K51" s="3" t="s">
@@ -6831,7 +6851,7 @@
       <c r="P51" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q51" s="4">
+      <c r="Q51" s="6">
         <v>922</v>
       </c>
       <c r="R51" s="4">
@@ -6941,7 +6961,7 @@
       <c r="P52" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q52" s="1" t="s">
+      <c r="Q52" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R52" s="1" t="s">
@@ -7030,7 +7050,7 @@
       <c r="I53" s="2">
         <v>46288</v>
       </c>
-      <c r="J53" s="8">
+      <c r="J53" s="6">
         <v>1199.67</v>
       </c>
       <c r="K53" s="3" t="s">
@@ -7051,7 +7071,7 @@
       <c r="P53" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q53" s="4">
+      <c r="Q53" s="6">
         <v>1199.67</v>
       </c>
       <c r="R53" s="4">
@@ -7140,7 +7160,7 @@
       <c r="I54" s="2">
         <v>46289</v>
       </c>
-      <c r="J54" s="8">
+      <c r="J54" s="6">
         <v>2500</v>
       </c>
       <c r="K54" s="3" t="s">
@@ -7161,7 +7181,7 @@
       <c r="P54" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="Q54" s="4">
+      <c r="Q54" s="6">
         <v>2500</v>
       </c>
       <c r="R54" s="4">
@@ -7250,7 +7270,7 @@
       <c r="I55" s="2">
         <v>46289</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="6">
         <v>14000</v>
       </c>
       <c r="K55" s="3" t="s">
@@ -7271,7 +7291,7 @@
       <c r="P55" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="Q55" s="4">
+      <c r="Q55" s="6">
         <v>14000</v>
       </c>
       <c r="R55" s="4">
@@ -7360,7 +7380,7 @@
       <c r="I56" s="2">
         <v>46289</v>
       </c>
-      <c r="J56" s="8">
+      <c r="J56" s="6">
         <v>5286.9</v>
       </c>
       <c r="K56" s="3" t="s">
@@ -7381,7 +7401,7 @@
       <c r="P56" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Q56" s="4">
+      <c r="Q56" s="6">
         <v>5286.9</v>
       </c>
       <c r="R56" s="4">
@@ -7470,7 +7490,7 @@
       <c r="I57" s="2">
         <v>46290</v>
       </c>
-      <c r="J57" s="8">
+      <c r="J57" s="6">
         <v>400</v>
       </c>
       <c r="K57" s="3" t="s">
@@ -7491,7 +7511,7 @@
       <c r="P57" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="Q57" s="4">
+      <c r="Q57" s="6">
         <v>400</v>
       </c>
       <c r="R57" s="4">
@@ -7580,7 +7600,7 @@
       <c r="I58" s="2">
         <v>46290</v>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="6">
         <v>700</v>
       </c>
       <c r="K58" s="3" t="s">
@@ -7601,7 +7621,7 @@
       <c r="P58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q58" s="4">
+      <c r="Q58" s="6">
         <v>700</v>
       </c>
       <c r="R58" s="4">
@@ -7711,7 +7731,7 @@
       <c r="P59" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q59" s="1" t="s">
+      <c r="Q59" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R59" s="1" t="s">
@@ -7800,7 +7820,7 @@
       <c r="I60" s="2">
         <v>46293</v>
       </c>
-      <c r="J60" s="8">
+      <c r="J60" s="6">
         <v>926.67</v>
       </c>
       <c r="K60" s="3" t="s">
@@ -7821,7 +7841,7 @@
       <c r="P60" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q60" s="4">
+      <c r="Q60" s="6">
         <v>926.67</v>
       </c>
       <c r="R60" s="4">
@@ -7910,7 +7930,7 @@
       <c r="I61" s="2">
         <v>46293</v>
       </c>
-      <c r="J61" s="8">
+      <c r="J61" s="6">
         <v>1828.43</v>
       </c>
       <c r="K61" s="3" t="s">
@@ -7931,7 +7951,7 @@
       <c r="P61" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="Q61" s="4">
+      <c r="Q61" s="6">
         <v>1828.43</v>
       </c>
       <c r="R61" s="4">
@@ -8020,7 +8040,7 @@
       <c r="I62" s="2">
         <v>46293</v>
       </c>
-      <c r="J62" s="8">
+      <c r="J62" s="6">
         <v>3100</v>
       </c>
       <c r="K62" s="3" t="s">
@@ -8041,7 +8061,7 @@
       <c r="P62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q62" s="4">
+      <c r="Q62" s="6">
         <v>3100</v>
       </c>
       <c r="R62" s="4">
@@ -8130,7 +8150,7 @@
       <c r="I63" s="2">
         <v>46295</v>
       </c>
-      <c r="J63" s="8">
+      <c r="J63" s="6">
         <v>3737.6</v>
       </c>
       <c r="K63" s="3" t="s">
@@ -8151,7 +8171,7 @@
       <c r="P63" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="Q63" s="4">
+      <c r="Q63" s="6">
         <v>3737.6</v>
       </c>
       <c r="R63" s="4">
@@ -8240,7 +8260,7 @@
       <c r="I64" s="2">
         <v>46295</v>
       </c>
-      <c r="J64" s="8">
+      <c r="J64" s="6">
         <v>5400</v>
       </c>
       <c r="K64" s="3" t="s">
@@ -8261,7 +8281,7 @@
       <c r="P64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q64" s="4">
+      <c r="Q64" s="6">
         <v>5400</v>
       </c>
       <c r="R64" s="4">
@@ -8350,7 +8370,7 @@
       <c r="I65" s="2">
         <v>46295</v>
       </c>
-      <c r="J65" s="8">
+      <c r="J65" s="6">
         <v>2200</v>
       </c>
       <c r="K65" s="3" t="s">
@@ -8371,7 +8391,7 @@
       <c r="P65" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="Q65" s="4">
+      <c r="Q65" s="6">
         <v>2200</v>
       </c>
       <c r="R65" s="4">
@@ -8481,7 +8501,7 @@
       <c r="P66" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q66" s="1" t="s">
+      <c r="Q66" s="7" t="s">
         <v>19</v>
       </c>
       <c r="R66" s="1" t="s">
@@ -8570,7 +8590,7 @@
       <c r="I67" s="2">
         <v>46300</v>
       </c>
-      <c r="J67" s="8">
+      <c r="J67" s="6">
         <v>1853.36</v>
       </c>
       <c r="K67" s="3" t="s">
@@ -8591,7 +8611,7 @@
       <c r="P67" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q67" s="4">
+      <c r="Q67" s="6">
         <v>1853.36</v>
       </c>
       <c r="R67" s="4">
@@ -8680,7 +8700,7 @@
       <c r="I68" s="2">
         <v>46308</v>
       </c>
-      <c r="J68" s="8">
+      <c r="J68" s="6">
         <v>3100</v>
       </c>
       <c r="K68" s="3" t="s">
@@ -8701,7 +8721,7 @@
       <c r="P68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q68" s="4">
+      <c r="Q68" s="6">
         <v>3100</v>
       </c>
       <c r="R68" s="4">
@@ -8790,7 +8810,7 @@
       <c r="I69" s="2">
         <v>46308</v>
       </c>
-      <c r="J69" s="8">
+      <c r="J69" s="6">
         <v>700</v>
       </c>
       <c r="K69" s="3" t="s">
@@ -8811,7 +8831,7 @@
       <c r="P69" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q69" s="4">
+      <c r="Q69" s="6">
         <v>700</v>
       </c>
       <c r="R69" s="4">
@@ -8900,7 +8920,7 @@
       <c r="I70" s="2">
         <v>46321</v>
       </c>
-      <c r="J70" s="8">
+      <c r="J70" s="6">
         <v>700</v>
       </c>
       <c r="K70" s="3" t="s">
@@ -8921,7 +8941,7 @@
       <c r="P70" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q70" s="4">
+      <c r="Q70" s="6">
         <v>700</v>
       </c>
       <c r="R70" s="4">
@@ -9010,7 +9030,7 @@
       <c r="I71" s="2">
         <v>46392</v>
       </c>
-      <c r="J71" s="8">
+      <c r="J71" s="6">
         <v>954</v>
       </c>
       <c r="K71" s="3" t="s">
@@ -9031,7 +9051,7 @@
       <c r="P71" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="Q71" s="4">
+      <c r="Q71" s="6">
         <v>954</v>
       </c>
       <c r="R71" s="4">
@@ -9120,7 +9140,7 @@
       <c r="I72" s="2">
         <v>46577</v>
       </c>
-      <c r="J72" s="8">
+      <c r="J72" s="6">
         <v>284</v>
       </c>
       <c r="K72" s="3" t="s">
@@ -9141,7 +9161,7 @@
       <c r="P72" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="Q72" s="4">
+      <c r="Q72" s="6">
         <v>284</v>
       </c>
       <c r="R72" s="4">
@@ -9203,17 +9223,20 @@
       </c>
     </row>
     <row r="75" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="J75" s="6">
-        <f>SUM(J5:J72)</f>
+      <c r="P75" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q75" s="6">
+        <f>SUM(Q5:Q72)</f>
         <v>173581.72</v>
       </c>
     </row>
     <row r="76" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="I76" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="J76" s="6">
-        <f>J75-J7-J8</f>
+      <c r="P76" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q76" s="6">
+        <f>Q75-Q7-Q8</f>
         <v>158218.22</v>
       </c>
     </row>
@@ -9224,5 +9247,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>